--- a/data/trans_bre/PCS12_SP_R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R3-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,12; 21,16</t>
+          <t>13,05; 20,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,79; 20,29</t>
+          <t>11,73; 20,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 19,98</t>
+          <t>10,35; 19,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,09; 20,74</t>
+          <t>11,15; 21,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,09; 70,89</t>
+          <t>38,32; 69,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,36; 61,69</t>
+          <t>30,28; 60,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,28; 60,05</t>
+          <t>26,65; 58,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,21; 50,37</t>
+          <t>23,01; 51,28</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,25</t>
+          <t>2,8; 6,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,06</t>
+          <t>3,38; 7,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,95</t>
+          <t>3,32; 7,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 3,65</t>
+          <t>-30,98; 3,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,84; 91,53</t>
+          <t>28,97; 89,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,54; 81,01</t>
+          <t>29,41; 81,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,15; 72,49</t>
+          <t>26,06; 72,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,07; 20,15</t>
+          <t>-65,15; 21,79</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,71</t>
+          <t>0,91; 8,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 4,57</t>
+          <t>-3,95; 3,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 8,01</t>
+          <t>0,3; 8,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 6,09</t>
+          <t>-0,56; 6,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,71; 145,71</t>
+          <t>9,92; 149,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 61,46</t>
+          <t>-34,35; 54,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 117,03</t>
+          <t>-0,98; 119,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 54,02</t>
+          <t>-3,99; 59,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,38</t>
+          <t>9,34; 13,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,1</t>
+          <t>9,29; 13,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 11,4</t>
+          <t>7,3; 11,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 7,68</t>
+          <t>-16,91; 7,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,57; 91,53</t>
+          <t>55,46; 90,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,09; 77,23</t>
+          <t>50,0; 80,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,47; 72,37</t>
+          <t>40,52; 72,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 35,89</t>
+          <t>-39,78; 36,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/PCS12_SP_R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R3-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,02</t>
+          <t>17,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,05; 20,66</t>
+          <t>12,93; 20,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,73; 20,27</t>
+          <t>12,0; 20,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,35; 19,72</t>
+          <t>10,21; 19,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 21,18</t>
+          <t>12,63; 22,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,32; 69,53</t>
+          <t>38,62; 71,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,28; 60,72</t>
+          <t>31,07; 60,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,65; 58,98</t>
+          <t>26,51; 57,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,01; 51,28</t>
+          <t>27,74; 56,49</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,54</t>
+          <t>5,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-24,05%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,99</t>
+          <t>2,55; 7,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,74</t>
+          <t>3,17; 7,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,94</t>
+          <t>3,37; 7,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 3,95</t>
+          <t>3,0; 7,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,97; 89,29</t>
+          <t>28,57; 92,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,41; 81,02</t>
+          <t>26,88; 80,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,06; 72,52</t>
+          <t>25,95; 72,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,15; 21,79</t>
+          <t>14,88; 44,83</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>3,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,72</t>
+          <t>1,17; 8,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 3,76</t>
+          <t>-4,13; 4,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 8,35</t>
+          <t>0,23; 8,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 6,41</t>
+          <t>0,61; 7,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 149,0</t>
+          <t>8,21; 145,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 54,4</t>
+          <t>-36,06; 54,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 119,31</t>
+          <t>1,69; 122,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 59,09</t>
+          <t>3,71; 65,1</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>9,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,56</t>
+          <t>9,48; 13,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,28</t>
+          <t>9,0; 13,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 11,5</t>
+          <t>7,32; 11,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 7,79</t>
+          <t>7,18; 10,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,46; 90,75</t>
+          <t>56,68; 90,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,0; 80,67</t>
+          <t>47,35; 78,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,52; 72,78</t>
+          <t>41,32; 73,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 36,33</t>
+          <t>32,1; 54,48</t>
         </is>
       </c>
     </row>
